--- a/Result/profitability/6767.xlsx
+++ b/Result/profitability/6767.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4367,6 +4367,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6767</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>84</v>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="n">
+        <v>64</v>
+      </c>
+      <c r="F32" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-1.72%</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.16875</v>
+      </c>
+      <c r="N32" t="n">
+        <v>78.005</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-2.111111111111111</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-3.350000000000009</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.04232469993682886</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.9900000000000091</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.01289230368537586</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
